--- a/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_01.xlsx
+++ b/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_01.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
   <si>
     <t>PAGO</t>
   </si>
@@ -55,19 +55,49 @@
     <t>DESCRIPCIÓN</t>
   </si>
   <si>
-    <t xml:space="preserve">RENE JAVIER MEDRANO LOPEZ  </t>
-  </si>
-  <si>
-    <t>012650028495052889</t>
+    <t xml:space="preserve">HECTOR JAVIER ARMANDO RODRIGUEZ VALDES  </t>
+  </si>
+  <si>
+    <t>002420903527668862</t>
   </si>
   <si>
     <t>PAGO SEMANA 33-2024</t>
   </si>
   <si>
+    <t>BANAMEX</t>
+  </si>
+  <si>
+    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>GERARDO DANIEL   HERMIDA AMADOR</t>
+  </si>
+  <si>
+    <t>AZTECA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
+  </si>
+  <si>
+    <t>012261004726315475</t>
+  </si>
+  <si>
     <t>BBVA MEXICO</t>
   </si>
   <si>
-    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
+    <t>2,836.00</t>
+  </si>
+  <si>
+    <t>2,586.42</t>
+  </si>
+  <si>
+    <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
+  </si>
+  <si>
+    <t>012320029389721173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
   </si>
   <si>
     <t>BENEFICIARIO</t>
@@ -83,6 +113,27 @@
   </si>
   <si>
     <t>CONCEPTO DE FACTURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ALBERTO LIN SALINAS  </t>
+  </si>
+  <si>
+    <t>LISL720802GW9</t>
+  </si>
+  <si>
+    <t>012180015558104539</t>
+  </si>
+  <si>
+    <t>IGNACIO  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>AOCI730717A95</t>
+  </si>
+  <si>
+    <t>012261011384032604</t>
+  </si>
+  <si>
+    <t>1,122.25</t>
   </si>
 </sst>
 </file>
@@ -425,19 +476,19 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="3.428" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="32.992" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="48.274" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="10" max="10" width="10.569" bestFit="true" customWidth="true" style="1"/>
     <col min="11" max="11" width="38.848" bestFit="true" customWidth="true" style="1"/>
     <col min="12" max="12" width="13.997" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -482,10 +533,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>49</v>
+        <v>5866</v>
       </c>
       <c r="B2">
-        <v>92</v>
+        <v>11101</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -503,15 +554,155 @@
         <v>15</v>
       </c>
       <c r="H2">
-        <v>390.23</v>
+        <v>600.0</v>
       </c>
       <c r="I2" s="1">
-        <v>17.27</v>
+        <v>30.7</v>
       </c>
       <c r="J2" s="1">
-        <v>372.96</v>
+        <v>569.3</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3">
+        <v>5864</v>
+      </c>
+      <c r="B3">
+        <v>17042</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>127290013759479947</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3">
+        <v>75.0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="J3" s="1">
+        <v>73.56</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4">
+        <v>5869</v>
+      </c>
+      <c r="B4">
+        <v>28842</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1">
+        <v>249.58</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5">
+        <v>5884</v>
+      </c>
+      <c r="B5">
+        <v>33949</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5">
+        <v>325.0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>13.1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>311.9</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6">
+        <v>5891</v>
+      </c>
+      <c r="B6">
+        <v>46264</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>127131013606487141</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>450.0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>428.9</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -527,21 +718,21 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="3.428" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="31.707" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="28.136" bestFit="true" customWidth="true" style="1"/>
     <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="6.998" bestFit="true" customWidth="true" style="1"/>
-    <col min="12" max="12" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="10.569" bestFit="true" customWidth="true" style="1"/>
+    <col min="12" max="12" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
@@ -553,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -568,13 +759,13 @@
         <v>8</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
@@ -583,7 +774,83 @@
         <v>11</v>
       </c>
       <c r="M1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2">
+        <v>5875</v>
+      </c>
+      <c r="B2">
+        <v>15862</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
         <v>21</v>
+      </c>
+      <c r="I2" s="1">
+        <v>312.5</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>312.5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <v>5868</v>
+      </c>
+      <c r="B3">
+        <v>32605</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_01.xlsx
+++ b/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_01.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>PAGO</t>
   </si>
@@ -28,122 +28,126 @@
     <t>SOCIO</t>
   </si>
   <si>
+    <t>CLABE</t>
+  </si>
+  <si>
+    <t>REF NUMÉRICA</t>
+  </si>
+  <si>
+    <t>REF ALFANUMÉRICA</t>
+  </si>
+  <si>
+    <t>BANCO</t>
+  </si>
+  <si>
+    <t>SUBTOTAL</t>
+  </si>
+  <si>
+    <t>ISR</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENE JAVIER MEDRANO LOPEZ  </t>
+  </si>
+  <si>
+    <t>012650028495052889</t>
+  </si>
+  <si>
+    <t>PAGO SEMANA 33-2024</t>
+  </si>
+  <si>
+    <t>BBVA MEXICO</t>
+  </si>
+  <si>
+    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HECTOR JAVIER ARMANDO RODRIGUEZ VALDES  </t>
+  </si>
+  <si>
+    <t>002420903527668862</t>
+  </si>
+  <si>
+    <t>BANAMEX</t>
+  </si>
+  <si>
+    <t>GERARDO DANIEL   HERMIDA AMADOR</t>
+  </si>
+  <si>
+    <t>AZTECA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA GUADALUPE VAZQUEZ FLORES  </t>
+  </si>
+  <si>
+    <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
+  </si>
+  <si>
+    <t>012320029389721173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
+  </si>
+  <si>
+    <t>BENEFICIARIO</t>
+  </si>
+  <si>
+    <t>IMPORTE</t>
+  </si>
+  <si>
+    <t>RETENCIÓN DE IVA 10.66%</t>
+  </si>
+  <si>
+    <t>IVA 16%</t>
+  </si>
+  <si>
+    <t>CONCEPTO DE FACTURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ALBERTO LIN SALINAS  </t>
+  </si>
+  <si>
+    <t>LISL720802GW9</t>
+  </si>
+  <si>
+    <t>012180015558104539</t>
+  </si>
+  <si>
+    <t>IGNACIO  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>AOCI730717A95</t>
+  </si>
+  <si>
+    <t>012261011384032604</t>
+  </si>
+  <si>
+    <t>EUGENIA  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>AOCE650713RL9</t>
+  </si>
+  <si>
+    <t>012261015099257013</t>
+  </si>
+  <si>
     <t>RFC</t>
-  </si>
-  <si>
-    <t>CLABE</t>
-  </si>
-  <si>
-    <t>REF NUMÉRICA</t>
-  </si>
-  <si>
-    <t>REF ALFANUMÉRICA</t>
-  </si>
-  <si>
-    <t>BANCO</t>
-  </si>
-  <si>
-    <t>SUBTOTAL</t>
-  </si>
-  <si>
-    <t>ISR</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>DESCRIPCIÓN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HECTOR JAVIER ARMANDO RODRIGUEZ VALDES  </t>
-  </si>
-  <si>
-    <t>002420903527668862</t>
-  </si>
-  <si>
-    <t>PAGO SEMANA 33-2024</t>
-  </si>
-  <si>
-    <t>BANAMEX</t>
-  </si>
-  <si>
-    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>GERARDO DANIEL   HERMIDA AMADOR</t>
-  </si>
-  <si>
-    <t>AZTECA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
-  </si>
-  <si>
-    <t>012261004726315475</t>
-  </si>
-  <si>
-    <t>BBVA MEXICO</t>
-  </si>
-  <si>
-    <t>2,836.00</t>
-  </si>
-  <si>
-    <t>2,586.42</t>
-  </si>
-  <si>
-    <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
-  </si>
-  <si>
-    <t>012320029389721173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
-  </si>
-  <si>
-    <t>BENEFICIARIO</t>
-  </si>
-  <si>
-    <t>IMPORTE</t>
-  </si>
-  <si>
-    <t>RETENCIÓN DE IVA 10.66%</t>
-  </si>
-  <si>
-    <t>IVA 16%</t>
-  </si>
-  <si>
-    <t>CONCEPTO DE FACTURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUIS ALBERTO LIN SALINAS  </t>
-  </si>
-  <si>
-    <t>LISL720802GW9</t>
-  </si>
-  <si>
-    <t>012180015558104539</t>
-  </si>
-  <si>
-    <t>IGNACIO  ALCOCER  CARVAJAL</t>
-  </si>
-  <si>
-    <t>AOCI730717A95</t>
-  </si>
-  <si>
-    <t>012261011384032604</t>
-  </si>
-  <si>
-    <t>1,122.25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -153,13 +157,28 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFffffff"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF009779"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -174,9 +193,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="165" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,234 +509,265 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="2"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="2"/>
     <col min="3" max="3" width="48.274" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="10.569" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="38.848" bestFit="true" customWidth="true" style="1"/>
-    <col min="12" max="12" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="24.565" bestFit="true" customWidth="true" style="3"/>
+    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="2"/>
+    <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="2"/>
+    <col min="7" max="7" width="16.282" bestFit="true" customWidth="true" style="2"/>
+    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="1"/>
+    <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="1"/>
+    <col min="11" max="11" width="38.848" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="2">
+        <v>11428</v>
+      </c>
+      <c r="B2" s="2">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2">
-        <v>5866</v>
-      </c>
-      <c r="B2">
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1">
+        <v>2531.95</v>
+      </c>
+      <c r="I2" s="1">
+        <v>202.45</v>
+      </c>
+      <c r="J2" s="1">
+        <v>2329.5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="2">
+        <v>11431</v>
+      </c>
+      <c r="B3" s="2">
         <v>11101</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1">
+        <v>675.0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="J3" s="1">
+        <v>639.5</v>
+      </c>
+      <c r="K3" t="s">
         <v>15</v>
       </c>
-      <c r="H2">
-        <v>600.0</v>
-      </c>
-      <c r="I2" s="1">
-        <v>30.7</v>
-      </c>
-      <c r="J2" s="1">
-        <v>569.3</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3">
-        <v>5864</v>
-      </c>
-      <c r="B3">
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2">
+        <v>11429</v>
+      </c>
+      <c r="B4" s="2">
         <v>17042</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3">
-        <v>127290013759479947</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3">
-        <v>75.0</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="J3" s="1">
-        <v>73.56</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4">
-        <v>5869</v>
-      </c>
-      <c r="B4">
-        <v>28842</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3">
+        <v>127290013759479947</v>
+      </c>
+      <c r="E4" s="2">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4">
+      <c r="H4" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="J4" s="1">
+        <v>73.56</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2">
+        <v>11432</v>
+      </c>
+      <c r="B5" s="2">
+        <v>25919</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3">
+        <v>127528013932219641</v>
+      </c>
+      <c r="E5" s="2">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1">
+        <v>31.35</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="J5" s="1">
+        <v>30.75</v>
+      </c>
+      <c r="K5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="2">
+        <v>11452</v>
+      </c>
+      <c r="B6" s="2">
+        <v>33949</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="1">
-        <v>249.58</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5">
-        <v>5884</v>
-      </c>
-      <c r="B5">
-        <v>33949</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="H6" s="1">
+        <v>425.0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="J6" s="1">
+        <v>405.5</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="2">
+        <v>11459</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46264</v>
+      </c>
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5">
+      <c r="D7" s="3">
+        <v>127131013606487141</v>
+      </c>
+      <c r="E7" s="2">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5">
-        <v>325.0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>13.1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>311.9</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6">
-        <v>5891</v>
-      </c>
-      <c r="B6">
-        <v>46264</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>127131013606487141</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6">
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1">
         <v>450.0</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I7" s="1">
         <v>21.1</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J7" s="1">
         <v>428.9</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>16</v>
+      <c r="K7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -718,10 +782,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="31.707" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
@@ -731,7 +795,7 @@
     <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="28.136" bestFit="true" customWidth="true" style="1"/>
     <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="10.569" bestFit="true" customWidth="true" style="1"/>
+    <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="1"/>
     <col min="12" max="12" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -744,113 +808,142 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
         <v>29</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2">
-        <v>5875</v>
+        <v>11440</v>
       </c>
       <c r="B2">
         <v>15862</v>
       </c>
       <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
       </c>
       <c r="F2">
         <v>30</v>
       </c>
       <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
       <c r="I2" s="1">
-        <v>312.5</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0.0</v>
+        <v>412.5</v>
       </c>
       <c r="K2" s="1">
-        <v>312.5</v>
+        <v>412.5</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3">
-        <v>5868</v>
+        <v>11435</v>
       </c>
       <c r="B3">
         <v>32605</v>
       </c>
       <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
         <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
       </c>
       <c r="F3">
         <v>30</v>
       </c>
       <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="1">
+        <v>872.75</v>
+      </c>
+      <c r="K3" s="1">
+        <v>872.75</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <v>11434</v>
+      </c>
+      <c r="B4">
+        <v>32614</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" t="s">
-        <v>16</v>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1080.0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1080.0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -893,31 +986,31 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_01.xlsx
+++ b/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_01.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>PAGO</t>
   </si>
@@ -52,19 +52,58 @@
     <t>DESCRIPCIÓN</t>
   </si>
   <si>
+    <t xml:space="preserve">BENJAMIN RAUL PADILLA BARRAGÁN  </t>
+  </si>
+  <si>
+    <t>002528700329964759</t>
+  </si>
+  <si>
+    <t>PAGO SEMANA 33-2024</t>
+  </si>
+  <si>
+    <t>BANAMEX</t>
+  </si>
+  <si>
+    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>IGNACIO  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>012261011384032604</t>
+  </si>
+  <si>
+    <t>BBVA MEXICO</t>
+  </si>
+  <si>
+    <t>EUGENIA  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>012261015099257013</t>
+  </si>
+  <si>
+    <t>BENEFICIARIO</t>
+  </si>
+  <si>
+    <t>IMPORTE</t>
+  </si>
+  <si>
+    <t>RET DE IVA 10.66%</t>
+  </si>
+  <si>
+    <t>IVA 16%</t>
+  </si>
+  <si>
+    <t>CONCEPTO DE FACTURA</t>
+  </si>
+  <si>
     <t xml:space="preserve">RENE JAVIER MEDRANO LOPEZ  </t>
   </si>
   <si>
     <t>012650028495052889</t>
   </si>
   <si>
-    <t>PAGO SEMANA 33-2024</t>
-  </si>
-  <si>
-    <t>BBVA MEXICO</t>
-  </si>
-  <si>
-    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
+    <t>PAGO DE COMISIONES</t>
   </si>
   <si>
     <t xml:space="preserve">HECTOR JAVIER ARMANDO RODRIGUEZ VALDES  </t>
@@ -73,70 +112,70 @@
     <t>002420903527668862</t>
   </si>
   <si>
-    <t>BANAMEX</t>
+    <t>LUCINA MARIA AURORA  RODRIGUEZ  MERIDA</t>
+  </si>
+  <si>
+    <t>012580028886932853</t>
   </si>
   <si>
     <t>GERARDO DANIEL   HERMIDA AMADOR</t>
   </si>
   <si>
-    <t>AZTECA</t>
-  </si>
-  <si>
     <t xml:space="preserve">MA GUADALUPE VAZQUEZ FLORES  </t>
   </si>
   <si>
+    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
+  </si>
+  <si>
+    <t>012261004726315475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIME GOMEZ SERRA  </t>
+  </si>
+  <si>
     <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
   </si>
   <si>
     <t>012320029389721173</t>
   </si>
   <si>
+    <t xml:space="preserve">PATRICIA ALCOCER CARVAJAL  </t>
+  </si>
+  <si>
+    <t>012261015561538956</t>
+  </si>
+  <si>
     <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
   </si>
   <si>
-    <t>BENEFICIARIO</t>
-  </si>
-  <si>
-    <t>IMPORTE</t>
-  </si>
-  <si>
-    <t>RETENCIÓN DE IVA 10.66%</t>
-  </si>
-  <si>
-    <t>IVA 16%</t>
-  </si>
-  <si>
-    <t>CONCEPTO DE FACTURA</t>
+    <t>CODIGO SAT</t>
+  </si>
+  <si>
+    <t>CONCEPTO FACTURA</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>DESC. BONIF. P-P BENELEIT</t>
+  </si>
+  <si>
+    <t>NETO</t>
+  </si>
+  <si>
+    <t>IVA</t>
+  </si>
+  <si>
+    <t>RET 1.25%</t>
+  </si>
+  <si>
+    <t>PROMOCIÓN, DISPOSICIÓN Y PUBLICIDAD VENTAS BENELEIT</t>
   </si>
   <si>
     <t xml:space="preserve">LUIS ALBERTO LIN SALINAS  </t>
   </si>
   <si>
-    <t>LISL720802GW9</t>
-  </si>
-  <si>
     <t>012180015558104539</t>
-  </si>
-  <si>
-    <t>IGNACIO  ALCOCER  CARVAJAL</t>
-  </si>
-  <si>
-    <t>AOCI730717A95</t>
-  </si>
-  <si>
-    <t>012261011384032604</t>
-  </si>
-  <si>
-    <t>EUGENIA  ALCOCER  CARVAJAL</t>
-  </si>
-  <si>
-    <t>AOCE650713RL9</t>
-  </si>
-  <si>
-    <t>012261015099257013</t>
-  </si>
-  <si>
-    <t>RFC</t>
   </si>
 </sst>
 </file>
@@ -144,8 +183,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#"/>
+    <numFmt numFmtId="164" formatCode="#"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -167,7 +206,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,6 +216,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF009779"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF192b5a"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -193,23 +238,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="165" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="164" fillId="2" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,19 +560,19 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="2"/>
-    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="2"/>
-    <col min="3" max="3" width="48.274" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="24.565" bestFit="true" customWidth="true" style="3"/>
-    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="2"/>
-    <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="2"/>
-    <col min="7" max="7" width="16.282" bestFit="true" customWidth="true" style="2"/>
-    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="1"/>
-    <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="1"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="3" max="3" width="38.848" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="23.423" bestFit="true" customWidth="true" style="2"/>
+    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="1"/>
+    <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="1"/>
+    <col min="7" max="7" width="16.282" bestFit="true" customWidth="true" style="1"/>
+    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="9" max="9" width="4.57" bestFit="true" customWidth="true" style="3"/>
+    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="3"/>
     <col min="11" max="11" width="38.848" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
@@ -561,212 +612,98 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="2">
-        <v>11428</v>
-      </c>
-      <c r="B2" s="2">
-        <v>92</v>
+      <c r="A2" s="1">
+        <v>11580</v>
+      </c>
+      <c r="B2" s="1">
+        <v>25918</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2">
-        <v>30</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="1">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1">
-        <v>2531.95</v>
-      </c>
-      <c r="I2" s="1">
-        <v>202.45</v>
-      </c>
-      <c r="J2" s="1">
-        <v>2329.5</v>
+      <c r="H2" s="3">
+        <v>908.08</v>
+      </c>
+      <c r="J2" s="3">
+        <v>908.08</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="2">
-        <v>11431</v>
-      </c>
-      <c r="B3" s="2">
-        <v>11101</v>
+      <c r="A3" s="1">
+        <v>11582</v>
+      </c>
+      <c r="B3" s="1">
+        <v>32605</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2">
-        <v>30</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="1">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1">
-        <v>675.0</v>
-      </c>
-      <c r="I3" s="1">
-        <v>35.5</v>
-      </c>
-      <c r="J3" s="1">
-        <v>639.5</v>
+      <c r="H3" s="3">
+        <v>872.75</v>
+      </c>
+      <c r="J3" s="3">
+        <v>872.75</v>
       </c>
       <c r="K3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="2">
-        <v>11429</v>
-      </c>
-      <c r="B4" s="2">
-        <v>17042</v>
+      <c r="A4" s="1">
+        <v>11581</v>
+      </c>
+      <c r="B4" s="1">
+        <v>32614</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="3">
-        <v>127290013759479947</v>
-      </c>
-      <c r="E4" s="2">
-        <v>30</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="1">
-        <v>75.0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="J4" s="1">
-        <v>73.56</v>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1080.0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1080.0</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="2">
-        <v>11432</v>
-      </c>
-      <c r="B5" s="2">
-        <v>25919</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="3">
-        <v>127528013932219641</v>
-      </c>
-      <c r="E5" s="2">
-        <v>30</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1">
-        <v>31.35</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="J5" s="1">
-        <v>30.75</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="2">
-        <v>11452</v>
-      </c>
-      <c r="B6" s="2">
-        <v>33949</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2">
-        <v>30</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="1">
-        <v>425.0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>19.5</v>
-      </c>
-      <c r="J6" s="1">
-        <v>405.5</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="2">
-        <v>11459</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46264</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3">
-        <v>127131013606487141</v>
-      </c>
-      <c r="E7" s="2">
-        <v>30</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="1">
-        <v>450.0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>21.1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>428.9</v>
-      </c>
-      <c r="K7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -782,168 +719,473 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="28.136" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="1"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="3" max="3" width="48.274" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="24.565" bestFit="true" customWidth="true" style="2"/>
+    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="1"/>
+    <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="1"/>
+    <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="8"/>
+    <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="9" max="9" width="21.138" bestFit="true" customWidth="true" style="3"/>
+    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="3"/>
     <col min="12" max="12" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="13" max="13" width="23.423" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1">
+        <v>11574</v>
+      </c>
+      <c r="B2" s="1">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2">
-        <v>11440</v>
-      </c>
-      <c r="B2">
-        <v>15862</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E2" s="1">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1">
-        <v>412.5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>412.5</v>
+      <c r="G2" s="8">
+        <v>1131.7327586207</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1312.81</v>
+      </c>
+      <c r="I2" s="3">
+        <v>120.64271206897</v>
+      </c>
+      <c r="J2" s="3">
+        <v>181.07724137931</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1192.167287931</v>
       </c>
       <c r="L2" t="s">
         <v>15</v>
       </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3">
-        <v>11435</v>
-      </c>
-      <c r="B3">
-        <v>32605</v>
+      <c r="A3" s="1">
+        <v>11577</v>
+      </c>
+      <c r="B3" s="1">
+        <v>11101</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="1">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1">
-        <v>872.75</v>
-      </c>
-      <c r="K3" s="1">
-        <v>872.75</v>
+      <c r="G3" s="8">
+        <v>581.89655172414</v>
+      </c>
+      <c r="H3" s="3">
+        <v>675.0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>62.030172413793</v>
+      </c>
+      <c r="J3" s="3">
+        <v>93.103448275862</v>
+      </c>
+      <c r="K3" s="3">
+        <v>612.96982758621</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
       </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4">
-        <v>11434</v>
-      </c>
-      <c r="B4">
-        <v>32614</v>
+      <c r="A4" s="1">
+        <v>11611</v>
+      </c>
+      <c r="B4" s="1">
+        <v>15432</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1080.0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1080.0</v>
+      <c r="G4" s="8">
+        <v>129.31034482759</v>
+      </c>
+      <c r="H4" s="3">
+        <v>150.0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>13.784482758621</v>
+      </c>
+      <c r="J4" s="3">
+        <v>20.689655172414</v>
+      </c>
+      <c r="K4" s="3">
+        <v>136.21551724138</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1">
+        <v>11575</v>
+      </c>
+      <c r="B5" s="1">
+        <v>17042</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2">
+        <v>127290013759479947</v>
+      </c>
+      <c r="E5" s="1">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="8">
+        <v>64.655172413793</v>
+      </c>
+      <c r="H5" s="3">
+        <v>75.0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>6.8922413793103</v>
+      </c>
+      <c r="J5" s="3">
+        <v>10.344827586207</v>
+      </c>
+      <c r="K5" s="3">
+        <v>68.10775862069</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1">
+        <v>11579</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25919</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2">
+        <v>127528013932219641</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="8">
+        <v>81.077586206897</v>
+      </c>
+      <c r="H6" s="3">
+        <v>94.05</v>
+      </c>
+      <c r="I6" s="3">
+        <v>8.6428706896552</v>
+      </c>
+      <c r="J6" s="3">
+        <v>12.972413793103</v>
+      </c>
+      <c r="K6" s="3">
+        <v>85.407129310345</v>
+      </c>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1">
+        <v>11590</v>
+      </c>
+      <c r="B7" s="1">
+        <v>28842</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1403.4482758621</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1628.0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>149.6075862069</v>
+      </c>
+      <c r="J7" s="3">
+        <v>224.55172413793</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1478.3924137931</v>
+      </c>
+      <c r="L7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1">
+        <v>11619</v>
+      </c>
+      <c r="B8" s="1">
+        <v>31624</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2">
+        <v>127854001413020886</v>
+      </c>
+      <c r="E8" s="1">
+        <v>30</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="8">
+        <v>74.310344827586</v>
+      </c>
+      <c r="H8" s="3">
+        <v>86.2</v>
+      </c>
+      <c r="I8" s="3">
+        <v>7.9214827586207</v>
+      </c>
+      <c r="J8" s="3">
+        <v>11.889655172414</v>
+      </c>
+      <c r="K8" s="3">
+        <v>78.278517241379</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1">
+        <v>11601</v>
+      </c>
+      <c r="B9" s="1">
+        <v>33949</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="8">
+        <v>366.37931034483</v>
+      </c>
+      <c r="H9" s="3">
+        <v>425.0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>39.056034482759</v>
+      </c>
+      <c r="J9" s="3">
+        <v>58.620689655172</v>
+      </c>
+      <c r="K9" s="3">
+        <v>385.94396551724</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1">
+        <v>11583</v>
+      </c>
+      <c r="B10" s="1">
+        <v>41929</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="1">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="8">
+        <v>1331.4224137931</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1544.45</v>
+      </c>
+      <c r="I10" s="3">
+        <v>141.92962931034</v>
+      </c>
+      <c r="J10" s="3">
+        <v>213.0275862069</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1402.5203706897</v>
+      </c>
+      <c r="L10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1">
+        <v>11610</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46264</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2">
+        <v>127131013606487141</v>
+      </c>
+      <c r="E11" s="1">
+        <v>30</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="8">
+        <v>387.93103448276</v>
+      </c>
+      <c r="H11" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>41.353448275862</v>
+      </c>
+      <c r="J11" s="3">
+        <v>62.068965517241</v>
+      </c>
+      <c r="K11" s="3">
+        <v>408.64655172414</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -958,59 +1200,125 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="5.856" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="3.428" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="4.57" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="1"/>
-    <col min="10" max="10" width="4.57" bestFit="true" customWidth="true" style="1"/>
-    <col min="11" max="11" width="6.998" bestFit="true" customWidth="true" style="1"/>
-    <col min="12" max="12" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="2" max="2" width="15.139" bestFit="true" customWidth="true" style="1"/>
+    <col min="3" max="3" width="63.556" bestFit="true" customWidth="true" style="1"/>
+    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="1"/>
+    <col min="5" max="5" width="31.707" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="2"/>
+    <col min="7" max="7" width="17.567" bestFit="true" customWidth="true" style="1"/>
+    <col min="8" max="8" width="25.708" bestFit="true" customWidth="true" style="1"/>
+    <col min="9" max="9" width="30.564" bestFit="true" customWidth="true" style="3"/>
+    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="11" max="11" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="12" max="12" width="10.569" bestFit="true" customWidth="true" style="3"/>
+    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="3"/>
+    <col min="14" max="14" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="15" max="15" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="16" max="16" width="38.848" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" s="5" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1">
+        <v>11588</v>
+      </c>
+      <c r="B2" s="1">
+        <v>80161701</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1">
+        <v>15862</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="1">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3">
+        <v>35.560344827586</v>
+      </c>
+      <c r="J2" s="3">
+        <v>412.5</v>
+      </c>
+      <c r="K2" s="3">
+        <v>355.60344827586</v>
+      </c>
+      <c r="L2" s="3">
+        <v>320.04310344828</v>
+      </c>
+      <c r="M2" s="3">
+        <v>51.206896551724</v>
+      </c>
+      <c r="N2" s="3">
+        <v>4.0005387931034</v>
+      </c>
+      <c r="O2" s="3">
+        <v>424.14601293103</v>
+      </c>
+      <c r="P2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_01.xlsx
+++ b/public_html/assets/archivo/corte/10-NUTRICION/10-NUTRICION_33-2024_01.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
   <si>
     <t>PAGO</t>
   </si>
@@ -52,130 +52,367 @@
     <t>DESCRIPCIÓN</t>
   </si>
   <si>
-    <t xml:space="preserve">BENJAMIN RAUL PADILLA BARRAGÁN  </t>
+    <t xml:space="preserve">CARMELA TABARES SOLTERO  </t>
+  </si>
+  <si>
+    <t>012320029099142851</t>
+  </si>
+  <si>
+    <t>PAGO SEMANA 33-2024</t>
+  </si>
+  <si>
+    <t>BBVA MEXICO</t>
+  </si>
+  <si>
+    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>GERMAN  PAZ  CASTRO</t>
+  </si>
+  <si>
+    <t>044580145023122636</t>
+  </si>
+  <si>
+    <t>SCOTIABANK</t>
+  </si>
+  <si>
+    <t>GRISELDA  AMEZCUA  ESPINOZA</t>
+  </si>
+  <si>
+    <t>002090700277605368</t>
+  </si>
+  <si>
+    <t>BANAMEX</t>
+  </si>
+  <si>
+    <t>RODOLFO  GALVEZ  BARRIOS</t>
+  </si>
+  <si>
+    <t>127540013217748396</t>
+  </si>
+  <si>
+    <t>AZTECA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA LORETO TORRES QUIRÓZ  </t>
+  </si>
+  <si>
+    <t>137667104892865788</t>
+  </si>
+  <si>
+    <t>BANCOPPEL</t>
+  </si>
+  <si>
+    <t>INOCENCIA  LOPEZ  LIZARDI</t>
+  </si>
+  <si>
+    <t>002320701583121645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRACIELA VARGAS FLORES  </t>
+  </si>
+  <si>
+    <t>002180701819195488</t>
+  </si>
+  <si>
+    <t>OLGA LORENA  GOMEZ  FOSADO</t>
+  </si>
+  <si>
+    <t>137290104379143332</t>
+  </si>
+  <si>
+    <t>LUCINA MARIA AURORA  RODRIGUEZ  MERIDA</t>
+  </si>
+  <si>
+    <t>012580028886932853</t>
+  </si>
+  <si>
+    <t>GERARDO DANIEL   HERMIDA AMADOR</t>
+  </si>
+  <si>
+    <t>127290013759479947</t>
+  </si>
+  <si>
+    <t>MA. ELIA  MENDEZ  PADRON</t>
+  </si>
+  <si>
+    <t>014700568624170380</t>
+  </si>
+  <si>
+    <t>SANTANDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEODEGARIA MENDEZ PADRON  </t>
+  </si>
+  <si>
+    <t>127700013552927500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARIO REYES LOPEZ  </t>
+  </si>
+  <si>
+    <t>002180701906484413</t>
+  </si>
+  <si>
+    <t>ESPERANZA GUADALUPE  BERNABE  PAZ</t>
+  </si>
+  <si>
+    <t>012098015082064800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA GUADALUPE VAZQUEZ FLORES  </t>
+  </si>
+  <si>
+    <t>127528013932219641</t>
+  </si>
+  <si>
+    <t>PAOLA ESMERALDA  PADILLA  VAZQUEZ</t>
+  </si>
+  <si>
+    <t>012528015519308774</t>
+  </si>
+  <si>
+    <t>PAULA JOSEFINA MARTINEZ  NAJERA</t>
+  </si>
+  <si>
+    <t>014261605958505324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONIA VILLASEÑOR CHAIREZ  </t>
+  </si>
+  <si>
+    <t>137095100128029149</t>
+  </si>
+  <si>
+    <t>OFELIA  TAMAYO  MEDRANO</t>
+  </si>
+  <si>
+    <t>127261013065980609</t>
+  </si>
+  <si>
+    <t>RUBEN  RODRIGUEZ SALINAS</t>
+  </si>
+  <si>
+    <t>137261101003307803</t>
+  </si>
+  <si>
+    <t>MARISELA  GUTIERREZ  RODRÍGUEZ</t>
+  </si>
+  <si>
+    <t>127320013929050325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASUNCION MARTINEZ MONTEJO  </t>
+  </si>
+  <si>
+    <t>127792013084267500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSALINDA CASTRO </t>
+  </si>
+  <si>
+    <t>012905027194030780</t>
+  </si>
+  <si>
+    <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
+  </si>
+  <si>
+    <t>012320029389721173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMA FILOMENA VILLASEÑOR ROMAN  </t>
+  </si>
+  <si>
+    <t>127320013081186470</t>
+  </si>
+  <si>
+    <t>ARACELI  NAVARRETE  MAYO</t>
+  </si>
+  <si>
+    <t>012261029126507460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA ALCOCER CARVAJAL  </t>
+  </si>
+  <si>
+    <t>012261015561538956</t>
+  </si>
+  <si>
+    <t>ANITA  RAMOS  PEREZ</t>
+  </si>
+  <si>
+    <t>012676028800563675</t>
+  </si>
+  <si>
+    <t>JOSE ROMULO  SANDOVAL  GUTIERREZ</t>
+  </si>
+  <si>
+    <t>012497015360493037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRISELDA MARIA ELENA RIOS LOPEZ  </t>
+  </si>
+  <si>
+    <t>002261701933654407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILBERTO VÁZQUEZ PÉREZ  </t>
+  </si>
+  <si>
+    <t>127798013739309568</t>
+  </si>
+  <si>
+    <t>EZEQUIEL   CAMAS  SALAYA</t>
+  </si>
+  <si>
+    <t>137798100490064414</t>
+  </si>
+  <si>
+    <t>RODOLFO  RODRIGUEZ  FERNANDEZ</t>
+  </si>
+  <si>
+    <t>002650902259397557</t>
+  </si>
+  <si>
+    <t>ANTONIA  GUZMAN  RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>127320013034432809</t>
+  </si>
+  <si>
+    <t>NATALIA ELIZABETH   GOMEZ   GUZMAN</t>
+  </si>
+  <si>
+    <t>072320012102620288</t>
+  </si>
+  <si>
+    <t>BANORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA MARIA DEL REFUGIO RODRIGUEZ BALANDRAN  </t>
+  </si>
+  <si>
+    <t>012180015397570366</t>
+  </si>
+  <si>
+    <t>MITZUQUI YAJAYRA  GALVÁN  ZARATE</t>
+  </si>
+  <si>
+    <t>137320104157672649</t>
+  </si>
+  <si>
+    <t>SARA LILIANE  RODRÍGUEZ  RUSCHKE</t>
+  </si>
+  <si>
+    <t>137100102403214627</t>
+  </si>
+  <si>
+    <t>JULISSA CAMACHO RAMIREZ</t>
+  </si>
+  <si>
+    <t>137130103802369375</t>
+  </si>
+  <si>
+    <t>BENEFICIARIO</t>
+  </si>
+  <si>
+    <t>IMPORTE</t>
+  </si>
+  <si>
+    <t>RET DE IVA 10.66%</t>
+  </si>
+  <si>
+    <t>IVA 16%</t>
+  </si>
+  <si>
+    <t>CONCEPTO DE FACTURA</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO  LIN  SALINAS</t>
+  </si>
+  <si>
+    <t>012180015558104539</t>
+  </si>
+  <si>
+    <t>PAGO DE COMISIONES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
+  </si>
+  <si>
+    <t>012261004726315475</t>
+  </si>
+  <si>
+    <t>IGNACIO  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>012261011384032604</t>
+  </si>
+  <si>
+    <t>EUGENIA  ALCOCER  CARVAJAL</t>
+  </si>
+  <si>
+    <t>012261015099257013</t>
+  </si>
+  <si>
+    <t>CODIGO SAT</t>
+  </si>
+  <si>
+    <t>CONCEPTO FACTURA</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>DESC. BONIF. P-P BENELEIT</t>
+  </si>
+  <si>
+    <t>NETO</t>
+  </si>
+  <si>
+    <t>IVA</t>
+  </si>
+  <si>
+    <t>RET 1.25%</t>
+  </si>
+  <si>
+    <t>PROMOCIÓN, DISPOSICIÓN Y PUBLICIDAD VENTAS BENELEIT</t>
+  </si>
+  <si>
+    <t>RENE JAVIER   MEDRANO LOPEZ</t>
+  </si>
+  <si>
+    <t>012650028495052889</t>
+  </si>
+  <si>
+    <t>MARIA DEL ROCIO  SALCEDO ROMERO</t>
+  </si>
+  <si>
+    <t>012650011174874447</t>
+  </si>
+  <si>
+    <t>ALMA ROSA BÁEZ  SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>002528701665393643</t>
+  </si>
+  <si>
+    <t>BENJAMIN RAUL  PADILLA  BARRAGÁN</t>
   </si>
   <si>
     <t>002528700329964759</t>
   </si>
   <si>
-    <t>PAGO SEMANA 33-2024</t>
-  </si>
-  <si>
-    <t>BANAMEX</t>
-  </si>
-  <si>
-    <t>DEL 12 DE AGOSTO AL 18 DE AGOSTO</t>
-  </si>
-  <si>
-    <t>IGNACIO  ALCOCER  CARVAJAL</t>
-  </si>
-  <si>
-    <t>012261011384032604</t>
-  </si>
-  <si>
-    <t>BBVA MEXICO</t>
-  </si>
-  <si>
-    <t>EUGENIA  ALCOCER  CARVAJAL</t>
-  </si>
-  <si>
-    <t>012261015099257013</t>
-  </si>
-  <si>
-    <t>BENEFICIARIO</t>
-  </si>
-  <si>
-    <t>IMPORTE</t>
-  </si>
-  <si>
-    <t>RET DE IVA 10.66%</t>
-  </si>
-  <si>
-    <t>IVA 16%</t>
-  </si>
-  <si>
-    <t>CONCEPTO DE FACTURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RENE JAVIER MEDRANO LOPEZ  </t>
-  </si>
-  <si>
-    <t>012650028495052889</t>
-  </si>
-  <si>
-    <t>PAGO DE COMISIONES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HECTOR JAVIER ARMANDO RODRIGUEZ VALDES  </t>
-  </si>
-  <si>
-    <t>002420903527668862</t>
-  </si>
-  <si>
-    <t>LUCINA MARIA AURORA  RODRIGUEZ  MERIDA</t>
-  </si>
-  <si>
-    <t>012580028886932853</t>
-  </si>
-  <si>
-    <t>GERARDO DANIEL   HERMIDA AMADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MA GUADALUPE VAZQUEZ FLORES  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFIA BARROSO RUIZ  </t>
-  </si>
-  <si>
-    <t>012261004726315475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAIME GOMEZ SERRA  </t>
-  </si>
-  <si>
-    <t>MARIA DE LA LUZ  MUÑOZ  CASTELLANOS</t>
-  </si>
-  <si>
-    <t>012320029389721173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATRICIA ALCOCER CARVAJAL  </t>
-  </si>
-  <si>
-    <t>012261015561538956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUEL DE JESUS CASTALDI PEREZ  </t>
-  </si>
-  <si>
-    <t>CODIGO SAT</t>
-  </si>
-  <si>
-    <t>CONCEPTO FACTURA</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>DESC. BONIF. P-P BENELEIT</t>
-  </si>
-  <si>
-    <t>NETO</t>
-  </si>
-  <si>
-    <t>IVA</t>
-  </si>
-  <si>
-    <t>RET 1.25%</t>
-  </si>
-  <si>
-    <t>PROMOCIÓN, DISPOSICIÓN Y PUBLICIDAD VENTAS BENELEIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUIS ALBERTO LIN SALINAS  </t>
-  </si>
-  <si>
-    <t>012180015558104539</t>
+    <t>CUQUIS  LARA  GARZA</t>
+  </si>
+  <si>
+    <t>002320070343371931</t>
+  </si>
+  <si>
+    <t>JAIME  GOMEZ  SERRA</t>
+  </si>
+  <si>
+    <t>127854001413020886</t>
   </si>
 </sst>
 </file>
@@ -560,18 +797,18 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="3" max="3" width="38.848" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="23.423" bestFit="true" customWidth="true" style="2"/>
+    <col min="2" max="2" width="10.426" bestFit="true" customWidth="true" style="1"/>
+    <col min="3" max="3" width="56.558" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="24.565" bestFit="true" customWidth="true" style="2"/>
     <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="1"/>
     <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="1"/>
     <col min="7" max="7" width="16.282" bestFit="true" customWidth="true" style="1"/>
     <col min="8" max="8" width="11.711" bestFit="true" customWidth="true" style="3"/>
-    <col min="9" max="9" width="4.57" bestFit="true" customWidth="true" style="3"/>
+    <col min="9" max="9" width="9.283" bestFit="true" customWidth="true" style="3"/>
     <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="3"/>
     <col min="11" max="11" width="38.848" bestFit="true" customWidth="true" style="0"/>
   </cols>
@@ -613,10 +850,10 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>11580</v>
+        <v>37588</v>
       </c>
       <c r="B2" s="1">
-        <v>25918</v>
+        <v>1373</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -634,10 +871,13 @@
         <v>14</v>
       </c>
       <c r="H2" s="3">
-        <v>908.08</v>
+        <v>104.0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>2.0</v>
       </c>
       <c r="J2" s="3">
-        <v>908.08</v>
+        <v>102.0</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
@@ -645,10 +885,10 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>11582</v>
+        <v>37615</v>
       </c>
       <c r="B3" s="1">
-        <v>32605</v>
+        <v>3146</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -666,10 +906,13 @@
         <v>18</v>
       </c>
       <c r="H3" s="3">
-        <v>872.75</v>
+        <v>150.0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>2.88</v>
       </c>
       <c r="J3" s="3">
-        <v>872.75</v>
+        <v>147.12</v>
       </c>
       <c r="K3" t="s">
         <v>15</v>
@@ -677,10 +920,10 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>11581</v>
+        <v>37610</v>
       </c>
       <c r="B4" s="1">
-        <v>32614</v>
+        <v>5841</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -695,15 +938,1278 @@
         <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3">
-        <v>1080.0</v>
+        <v>600.0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>30.7</v>
       </c>
       <c r="J4" s="3">
-        <v>1080.0</v>
+        <v>569.3</v>
       </c>
       <c r="K4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1">
+        <v>37602</v>
+      </c>
+      <c r="B5" s="1">
+        <v>7815</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="3">
+        <v>103.0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="J5" s="3">
+        <v>101.02</v>
+      </c>
+      <c r="K5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1">
+        <v>37598</v>
+      </c>
+      <c r="B6" s="1">
+        <v>8272</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="3">
+        <v>824.0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>45.03</v>
+      </c>
+      <c r="J6" s="3">
+        <v>778.97</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1">
+        <v>37595</v>
+      </c>
+      <c r="B7" s="1">
+        <v>9040</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="3">
+        <v>249.0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>8.23</v>
+      </c>
+      <c r="J7" s="3">
+        <v>240.77</v>
+      </c>
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="1">
+        <v>37568</v>
+      </c>
+      <c r="B8" s="1">
+        <v>12634</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="1">
+        <v>30</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="3">
+        <v>125.0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="J8" s="3">
+        <v>122.6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1">
+        <v>37590</v>
+      </c>
+      <c r="B9" s="1">
+        <v>14975</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="3">
+        <v>75.0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="J9" s="3">
+        <v>73.56</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1">
+        <v>37614</v>
+      </c>
+      <c r="B10" s="1">
+        <v>15432</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>21.1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>428.9</v>
+      </c>
+      <c r="K10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1">
+        <v>37589</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17042</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="1">
+        <v>30</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="3">
+        <v>75.0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="J11" s="3">
+        <v>73.56</v>
+      </c>
+      <c r="K11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1">
+        <v>37612</v>
+      </c>
+      <c r="B12" s="1">
+        <v>18735</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="3">
+        <v>84.0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1.61</v>
+      </c>
+      <c r="J12" s="3">
+        <v>82.39</v>
+      </c>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="1">
+        <v>37611</v>
+      </c>
+      <c r="B13" s="1">
+        <v>18791</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="1">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="J13" s="3">
+        <v>27.46</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1">
+        <v>37576</v>
+      </c>
+      <c r="B14" s="1">
+        <v>20416</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="1">
+        <v>30</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="3">
+        <v>823.0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>44.97</v>
+      </c>
+      <c r="J14" s="3">
+        <v>778.03</v>
+      </c>
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="1">
+        <v>37609</v>
+      </c>
+      <c r="B15" s="1">
+        <v>20738</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="1">
+        <v>30</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="3">
+        <v>225.0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="J15" s="3">
+        <v>218.3</v>
+      </c>
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="1">
+        <v>37567</v>
+      </c>
+      <c r="B16" s="1">
+        <v>25919</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="1">
+        <v>30</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="3">
+        <v>478.05</v>
+      </c>
+      <c r="I16" s="3">
+        <v>22.89</v>
+      </c>
+      <c r="J16" s="3">
+        <v>455.16</v>
+      </c>
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="1">
+        <v>37566</v>
+      </c>
+      <c r="B17" s="1">
+        <v>28629</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="1">
+        <v>30</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="3">
+        <v>134.35</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2.58</v>
+      </c>
+      <c r="J17" s="3">
+        <v>131.77</v>
+      </c>
+      <c r="K17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="1">
+        <v>37571</v>
+      </c>
+      <c r="B18" s="1">
+        <v>30292</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="1">
+        <v>30</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="3">
+        <v>878.0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>48.49</v>
+      </c>
+      <c r="J18" s="3">
+        <v>829.51</v>
+      </c>
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="1">
+        <v>37562</v>
+      </c>
+      <c r="B19" s="1">
+        <v>30656</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="3">
+        <v>75.0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="J19" s="3">
+        <v>73.56</v>
+      </c>
+      <c r="K19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="1">
+        <v>37570</v>
+      </c>
+      <c r="B20" s="1">
+        <v>31574</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="1">
+        <v>30</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="3">
+        <v>354.25</v>
+      </c>
+      <c r="I20" s="3">
+        <v>14.97</v>
+      </c>
+      <c r="J20" s="3">
+        <v>339.28</v>
+      </c>
+      <c r="K20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="1">
+        <v>37569</v>
+      </c>
+      <c r="B21" s="1">
+        <v>31689</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="1">
+        <v>30</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="3">
+        <v>84.75</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1.63</v>
+      </c>
+      <c r="J21" s="3">
+        <v>83.12</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="1">
+        <v>37582</v>
+      </c>
+      <c r="B22" s="1">
+        <v>31758</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="1">
+        <v>30</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1614.0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>102.58</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1511.42</v>
+      </c>
+      <c r="K22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="1">
+        <v>37579</v>
+      </c>
+      <c r="B23" s="1">
+        <v>32042</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="1">
+        <v>30</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="3">
+        <v>620.8</v>
+      </c>
+      <c r="I23" s="3">
+        <v>32.03</v>
+      </c>
+      <c r="J23" s="3">
+        <v>588.77</v>
+      </c>
+      <c r="K23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="1">
+        <v>37583</v>
+      </c>
+      <c r="B24" s="1">
+        <v>32907</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="1">
+        <v>30</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="3">
+        <v>75.0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1.44</v>
+      </c>
+      <c r="J24" s="3">
+        <v>73.56</v>
+      </c>
+      <c r="K24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="1">
+        <v>37581</v>
+      </c>
+      <c r="B25" s="1">
+        <v>33949</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="1">
+        <v>30</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="3">
+        <v>655.25</v>
+      </c>
+      <c r="I25" s="3">
+        <v>34.23</v>
+      </c>
+      <c r="J25" s="3">
+        <v>621.02</v>
+      </c>
+      <c r="K25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="1">
+        <v>37580</v>
+      </c>
+      <c r="B26" s="1">
+        <v>34105</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="1">
+        <v>30</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="3">
+        <v>351.75</v>
+      </c>
+      <c r="I26" s="3">
+        <v>14.81</v>
+      </c>
+      <c r="J26" s="3">
+        <v>336.94</v>
+      </c>
+      <c r="K26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="1">
+        <v>37604</v>
+      </c>
+      <c r="B27" s="1">
+        <v>35912</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="1">
+        <v>30</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1467.5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>86.64</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1380.86</v>
+      </c>
+      <c r="K27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="1">
+        <v>37585</v>
+      </c>
+      <c r="B28" s="1">
+        <v>41929</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="3">
+        <v>2144.45</v>
+      </c>
+      <c r="I28" s="3">
+        <v>160.29</v>
+      </c>
+      <c r="J28" s="3">
+        <v>1984.16</v>
+      </c>
+      <c r="K28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="1">
+        <v>37596</v>
+      </c>
+      <c r="B29" s="1">
+        <v>42170</v>
+      </c>
+      <c r="C29" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="1">
+        <v>30</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="3">
+        <v>413.5</v>
+      </c>
+      <c r="I29" s="3">
+        <v>18.76</v>
+      </c>
+      <c r="J29" s="3">
+        <v>394.74</v>
+      </c>
+      <c r="K29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="1">
+        <v>37574</v>
+      </c>
+      <c r="B30" s="1">
+        <v>45670</v>
+      </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="1">
+        <v>30</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="3">
+        <v>357.5</v>
+      </c>
+      <c r="I30" s="3">
+        <v>15.18</v>
+      </c>
+      <c r="J30" s="3">
+        <v>342.32</v>
+      </c>
+      <c r="K30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="1">
+        <v>37603</v>
+      </c>
+      <c r="B31" s="1">
+        <v>48056</v>
+      </c>
+      <c r="C31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="1">
+        <v>30</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="3">
+        <v>563.25</v>
+      </c>
+      <c r="I31" s="3">
+        <v>28.34</v>
+      </c>
+      <c r="J31" s="3">
+        <v>534.91</v>
+      </c>
+      <c r="K31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="1">
+        <v>37578</v>
+      </c>
+      <c r="B32" s="1">
+        <v>50496</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="1">
+        <v>30</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="3">
+        <v>232.8</v>
+      </c>
+      <c r="I32" s="3">
+        <v>7.19</v>
+      </c>
+      <c r="J32" s="3">
+        <v>225.61</v>
+      </c>
+      <c r="K32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="1">
+        <v>37577</v>
+      </c>
+      <c r="B33" s="1">
+        <v>58634</v>
+      </c>
+      <c r="C33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="1">
+        <v>30</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="3">
+        <v>77.6</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="J33" s="3">
+        <v>76.11</v>
+      </c>
+      <c r="K33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="1">
+        <v>37600</v>
+      </c>
+      <c r="B34" s="1">
+        <v>63848</v>
+      </c>
+      <c r="C34" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="1">
+        <v>30</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="J34" s="3">
+        <v>24.52</v>
+      </c>
+      <c r="K34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="1">
+        <v>37594</v>
+      </c>
+      <c r="B35" s="1">
+        <v>131240</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="1">
+        <v>30</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="3">
+        <v>537.6</v>
+      </c>
+      <c r="I35" s="3">
+        <v>26.7</v>
+      </c>
+      <c r="J35" s="3">
+        <v>510.9</v>
+      </c>
+      <c r="K35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="1">
+        <v>37593</v>
+      </c>
+      <c r="B36" s="1">
+        <v>133002</v>
+      </c>
+      <c r="C36" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="1">
+        <v>30</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H36" s="3">
+        <v>89.0</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1.71</v>
+      </c>
+      <c r="J36" s="3">
+        <v>87.29</v>
+      </c>
+      <c r="K36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="1">
+        <v>37592</v>
+      </c>
+      <c r="B37" s="1">
+        <v>156888</v>
+      </c>
+      <c r="C37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E37" s="1">
+        <v>30</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="3">
+        <v>67.0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1.29</v>
+      </c>
+      <c r="J37" s="3">
+        <v>65.71</v>
+      </c>
+      <c r="K37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="1">
+        <v>37618</v>
+      </c>
+      <c r="B38" s="1">
+        <v>157530</v>
+      </c>
+      <c r="C38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="1">
+        <v>30</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="3">
+        <v>152.0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>2.92</v>
+      </c>
+      <c r="J38" s="3">
+        <v>149.08</v>
+      </c>
+      <c r="K38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="1">
+        <v>37616</v>
+      </c>
+      <c r="B39" s="1">
+        <v>158701</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="1">
+        <v>30</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="3">
+        <v>675.0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>35.5</v>
+      </c>
+      <c r="J39" s="3">
+        <v>639.5</v>
+      </c>
+      <c r="K39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="1">
+        <v>37619</v>
+      </c>
+      <c r="B40" s="1">
+        <v>158844</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="1">
+        <v>30</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H40" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>5.1</v>
+      </c>
+      <c r="J40" s="3">
+        <v>194.9</v>
+      </c>
+      <c r="K40" t="s">
         <v>15</v>
       </c>
     </row>
@@ -719,13 +2225,13 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
     <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="3" max="3" width="48.274" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="24.565" bestFit="true" customWidth="true" style="2"/>
+    <col min="3" max="3" width="31.707" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="23.423" bestFit="true" customWidth="true" style="2"/>
     <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="1"/>
     <col min="6" max="6" width="25.708" bestFit="true" customWidth="true" style="1"/>
     <col min="7" max="7" width="13.997" bestFit="true" customWidth="true" style="8"/>
@@ -745,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>3</v>
@@ -760,13 +2266,13 @@
         <v>7</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>9</v>
@@ -775,21 +2281,21 @@
         <v>10</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1">
-        <v>11574</v>
+        <v>37597</v>
       </c>
       <c r="B2" s="1">
-        <v>92</v>
+        <v>15862</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -798,39 +2304,39 @@
         <v>13</v>
       </c>
       <c r="G2" s="8">
-        <v>1131.7327586207</v>
+        <v>355.60344827586</v>
       </c>
       <c r="H2" s="3">
-        <v>1312.81</v>
+        <v>412.5</v>
       </c>
       <c r="I2" s="3">
-        <v>120.64271206897</v>
+        <v>37.907327586207</v>
       </c>
       <c r="J2" s="3">
-        <v>181.07724137931</v>
+        <v>56.896551724138</v>
       </c>
       <c r="K2" s="3">
-        <v>1192.167287931</v>
+        <v>374.59267241379</v>
       </c>
       <c r="L2" t="s">
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1">
-        <v>11577</v>
+        <v>37599</v>
       </c>
       <c r="B3" s="1">
-        <v>11101</v>
+        <v>28842</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -839,39 +2345,39 @@
         <v>13</v>
       </c>
       <c r="G3" s="8">
-        <v>581.89655172414</v>
+        <v>1907.8017241379</v>
       </c>
       <c r="H3" s="3">
-        <v>675.0</v>
+        <v>2213.05</v>
       </c>
       <c r="I3" s="3">
-        <v>62.030172413793</v>
+        <v>203.3716637931</v>
       </c>
       <c r="J3" s="3">
-        <v>93.103448275862</v>
+        <v>305.24827586207</v>
       </c>
       <c r="K3" s="3">
-        <v>612.96982758621</v>
+        <v>2009.6783362069</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
-        <v>11611</v>
+        <v>37584</v>
       </c>
       <c r="B4" s="1">
-        <v>15432</v>
+        <v>32605</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="E4" s="1">
         <v>30</v>
@@ -880,39 +2386,39 @@
         <v>13</v>
       </c>
       <c r="G4" s="8">
-        <v>129.31034482759</v>
+        <v>946.33620689655</v>
       </c>
       <c r="H4" s="3">
-        <v>150.0</v>
+        <v>1097.75</v>
       </c>
       <c r="I4" s="3">
-        <v>13.784482758621</v>
+        <v>100.87943965517</v>
       </c>
       <c r="J4" s="3">
-        <v>20.689655172414</v>
+        <v>151.41379310345</v>
       </c>
       <c r="K4" s="3">
-        <v>136.21551724138</v>
+        <v>996.87056034483</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1">
-        <v>11575</v>
+        <v>37591</v>
       </c>
       <c r="B5" s="1">
-        <v>17042</v>
+        <v>32614</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="2">
-        <v>127290013759479947</v>
+        <v>110</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="E5" s="1">
         <v>30</v>
@@ -921,271 +2427,25 @@
         <v>13</v>
       </c>
       <c r="G5" s="8">
-        <v>64.655172413793</v>
+        <v>931.03448275862</v>
       </c>
       <c r="H5" s="3">
-        <v>75.0</v>
+        <v>1080.0</v>
       </c>
       <c r="I5" s="3">
-        <v>6.8922413793103</v>
+        <v>99.248275862069</v>
       </c>
       <c r="J5" s="3">
-        <v>10.344827586207</v>
+        <v>148.96551724138</v>
       </c>
       <c r="K5" s="3">
-        <v>68.10775862069</v>
+        <v>980.75172413793</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1">
-        <v>11579</v>
-      </c>
-      <c r="B6" s="1">
-        <v>25919</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="2">
-        <v>127528013932219641</v>
-      </c>
-      <c r="E6" s="1">
-        <v>30</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="8">
-        <v>81.077586206897</v>
-      </c>
-      <c r="H6" s="3">
-        <v>94.05</v>
-      </c>
-      <c r="I6" s="3">
-        <v>8.6428706896552</v>
-      </c>
-      <c r="J6" s="3">
-        <v>12.972413793103</v>
-      </c>
-      <c r="K6" s="3">
-        <v>85.407129310345</v>
-      </c>
-      <c r="L6" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1">
-        <v>11590</v>
-      </c>
-      <c r="B7" s="1">
-        <v>28842</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="1">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1403.4482758621</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1628.0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>149.6075862069</v>
-      </c>
-      <c r="J7" s="3">
-        <v>224.55172413793</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1478.3924137931</v>
-      </c>
-      <c r="L7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1">
-        <v>11619</v>
-      </c>
-      <c r="B8" s="1">
-        <v>31624</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="2">
-        <v>127854001413020886</v>
-      </c>
-      <c r="E8" s="1">
-        <v>30</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="8">
-        <v>74.310344827586</v>
-      </c>
-      <c r="H8" s="3">
-        <v>86.2</v>
-      </c>
-      <c r="I8" s="3">
-        <v>7.9214827586207</v>
-      </c>
-      <c r="J8" s="3">
-        <v>11.889655172414</v>
-      </c>
-      <c r="K8" s="3">
-        <v>78.278517241379</v>
-      </c>
-      <c r="L8" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1">
-        <v>11601</v>
-      </c>
-      <c r="B9" s="1">
-        <v>33949</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="1">
-        <v>30</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="8">
-        <v>366.37931034483</v>
-      </c>
-      <c r="H9" s="3">
-        <v>425.0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>39.056034482759</v>
-      </c>
-      <c r="J9" s="3">
-        <v>58.620689655172</v>
-      </c>
-      <c r="K9" s="3">
-        <v>385.94396551724</v>
-      </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1">
-        <v>11583</v>
-      </c>
-      <c r="B10" s="1">
-        <v>41929</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="1">
-        <v>30</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1331.4224137931</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1544.45</v>
-      </c>
-      <c r="I10" s="3">
-        <v>141.92962931034</v>
-      </c>
-      <c r="J10" s="3">
-        <v>213.0275862069</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1402.5203706897</v>
-      </c>
-      <c r="L10" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1">
-        <v>11610</v>
-      </c>
-      <c r="B11" s="1">
-        <v>46264</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="2">
-        <v>127131013606487141</v>
-      </c>
-      <c r="E11" s="1">
-        <v>30</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="8">
-        <v>387.93103448276</v>
-      </c>
-      <c r="H11" s="3">
-        <v>450.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>41.353448275862</v>
-      </c>
-      <c r="J11" s="3">
-        <v>62.068965517241</v>
-      </c>
-      <c r="K11" s="3">
-        <v>408.64655172414</v>
-      </c>
-      <c r="L11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1200,24 +2460,24 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
     <col min="2" max="2" width="15.139" bestFit="true" customWidth="true" style="1"/>
     <col min="3" max="3" width="63.556" bestFit="true" customWidth="true" style="1"/>
     <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="1"/>
-    <col min="5" max="5" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="2"/>
+    <col min="5" max="5" width="38.848" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="24.565" bestFit="true" customWidth="true" style="2"/>
     <col min="7" max="7" width="17.567" bestFit="true" customWidth="true" style="1"/>
     <col min="8" max="8" width="25.708" bestFit="true" customWidth="true" style="1"/>
     <col min="9" max="9" width="30.564" bestFit="true" customWidth="true" style="3"/>
-    <col min="10" max="10" width="9.283" bestFit="true" customWidth="true" style="3"/>
-    <col min="11" max="11" width="9.283" bestFit="true" customWidth="true" style="3"/>
-    <col min="12" max="12" width="10.569" bestFit="true" customWidth="true" style="3"/>
-    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="3"/>
+    <col min="10" max="10" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="12" max="12" width="11.711" bestFit="true" customWidth="true" style="3"/>
+    <col min="13" max="13" width="9.283" bestFit="true" customWidth="true" style="3"/>
     <col min="14" max="14" width="11.711" bestFit="true" customWidth="true" style="3"/>
-    <col min="15" max="15" width="9.283" bestFit="true" customWidth="true" style="3"/>
+    <col min="15" max="15" width="11.711" bestFit="true" customWidth="true" style="3"/>
     <col min="16" max="16" width="38.848" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
@@ -1226,13 +2486,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -1247,22 +2507,22 @@
         <v>5</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>9</v>
@@ -1273,22 +2533,22 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1">
-        <v>11588</v>
+        <v>37563</v>
       </c>
       <c r="B2" s="1">
         <v>80161701</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="D2" s="1">
-        <v>15862</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="G2" s="1">
         <v>30</v>
@@ -1297,27 +2557,277 @@
         <v>13</v>
       </c>
       <c r="I2" s="3">
-        <v>35.560344827586</v>
+        <v>223.44913793103</v>
       </c>
       <c r="J2" s="3">
-        <v>412.5</v>
+        <v>2592.01</v>
       </c>
       <c r="K2" s="3">
-        <v>355.60344827586</v>
+        <v>2234.4913793103</v>
       </c>
       <c r="L2" s="3">
-        <v>320.04310344828</v>
+        <v>2011.0422413793</v>
       </c>
       <c r="M2" s="3">
-        <v>51.206896551724</v>
+        <v>321.76675862069</v>
       </c>
       <c r="N2" s="3">
-        <v>4.0005387931034</v>
+        <v>25.138028017241</v>
       </c>
       <c r="O2" s="3">
-        <v>424.14601293103</v>
+        <v>2665.1895926724</v>
       </c>
       <c r="P2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1">
+        <v>37587</v>
+      </c>
+      <c r="B3" s="1">
+        <v>80161701</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="1">
+        <v>10859</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="1">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3">
+        <v>88.396551724138</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1025.4</v>
+      </c>
+      <c r="K3" s="3">
+        <v>883.96551724138</v>
+      </c>
+      <c r="L3" s="3">
+        <v>795.56896551724</v>
+      </c>
+      <c r="M3" s="3">
+        <v>127.29103448276</v>
+      </c>
+      <c r="N3" s="3">
+        <v>9.9446120689655</v>
+      </c>
+      <c r="O3" s="3">
+        <v>1054.3498706897</v>
+      </c>
+      <c r="P3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1">
+        <v>37607</v>
+      </c>
+      <c r="B4" s="1">
+        <v>80161701</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="1">
+        <v>17507</v>
+      </c>
+      <c r="E4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="1">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3">
+        <v>76.193965517241</v>
+      </c>
+      <c r="J4" s="3">
+        <v>883.85</v>
+      </c>
+      <c r="K4" s="3">
+        <v>761.93965517241</v>
+      </c>
+      <c r="L4" s="3">
+        <v>685.74568965517</v>
+      </c>
+      <c r="M4" s="3">
+        <v>109.71931034483</v>
+      </c>
+      <c r="N4" s="3">
+        <v>8.5718211206897</v>
+      </c>
+      <c r="O4" s="3">
+        <v>908.8035237069</v>
+      </c>
+      <c r="P4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="1">
+        <v>37572</v>
+      </c>
+      <c r="B5" s="1">
+        <v>80161701</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="1">
+        <v>25918</v>
+      </c>
+      <c r="E5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="1">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="3">
+        <v>122.75172413793</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1423.92</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1227.5172413793</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1104.7655172414</v>
+      </c>
+      <c r="M5" s="3">
+        <v>176.76248275862</v>
+      </c>
+      <c r="N5" s="3">
+        <v>13.809568965517</v>
+      </c>
+      <c r="O5" s="3">
+        <v>1464.1211896552</v>
+      </c>
+      <c r="P5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="1">
+        <v>37606</v>
+      </c>
+      <c r="B6" s="1">
+        <v>80161701</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="1">
+        <v>31622</v>
+      </c>
+      <c r="E6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="1">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="3">
+        <v>27.071551724138</v>
+      </c>
+      <c r="J6" s="3">
+        <v>314.03</v>
+      </c>
+      <c r="K6" s="3">
+        <v>270.71551724138</v>
+      </c>
+      <c r="L6" s="3">
+        <v>243.64396551724</v>
+      </c>
+      <c r="M6" s="3">
+        <v>38.983034482759</v>
+      </c>
+      <c r="N6" s="3">
+        <v>3.0455495689655</v>
+      </c>
+      <c r="O6" s="3">
+        <v>322.89593318966</v>
+      </c>
+      <c r="P6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="1">
+        <v>37621</v>
+      </c>
+      <c r="B7" s="1">
+        <v>80161701</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="1">
+        <v>31624</v>
+      </c>
+      <c r="E7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="1">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="3">
+        <v>14.120689655172</v>
+      </c>
+      <c r="J7" s="3">
+        <v>163.8</v>
+      </c>
+      <c r="K7" s="3">
+        <v>141.20689655172</v>
+      </c>
+      <c r="L7" s="3">
+        <v>127.08620689655</v>
+      </c>
+      <c r="M7" s="3">
+        <v>20.333793103448</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1.5885775862069</v>
+      </c>
+      <c r="O7" s="3">
+        <v>168.42452586207</v>
+      </c>
+      <c r="P7" t="s">
         <v>15</v>
       </c>
     </row>
